--- a/results_cnn_evaluation(stress_test)/cnn_cnn_evaluation(stress_test)_fussion_type-sigmoid_gating_k-100_tau-0.3_normalization-True.xlsx
+++ b/results_cnn_evaluation(stress_test)/cnn_cnn_evaluation(stress_test)_fussion_type-sigmoid_gating_k-100_tau-0.3_normalization-True.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="nrr_0.3" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="nrr_0.5" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="nrr_0.2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="nrr_0.1" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="nrr_0.5" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="nrr_0.3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="nrr_0.2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="nrr_0.1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="nrr_0.05" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -466,16 +467,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>84.66076696165192</v>
+        <v>88.96755162241888</v>
       </c>
       <c r="C2" t="n">
-        <v>84.64470229803298</v>
+        <v>88.00092768917392</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3857169011762987</v>
+        <v>0.358489412075869</v>
       </c>
       <c r="E2" t="n">
-        <v>84.66076696165192</v>
+        <v>88.96755162241888</v>
       </c>
     </row>
     <row r="3">
@@ -485,16 +486,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>87.52212389380531</v>
+        <v>90.94395280235987</v>
       </c>
       <c r="C3" t="n">
-        <v>85.89044098203433</v>
+        <v>90.37213964784107</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4172976872689712</v>
+        <v>0.2919561577999654</v>
       </c>
       <c r="E3" t="n">
-        <v>87.5221238938053</v>
+        <v>90.94395280235987</v>
       </c>
     </row>
     <row r="4">
@@ -504,16 +505,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>85.45740015052033</v>
+        <v>88.61356932153392</v>
       </c>
       <c r="C4" t="n">
-        <v>84.41127414960694</v>
+        <v>87.61164303140852</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4649138840812762</v>
+        <v>0.3680214273867023</v>
       </c>
       <c r="E4" t="n">
-        <v>85.45740015052033</v>
+        <v>88.61356932153392</v>
       </c>
     </row>
     <row r="5">
@@ -523,16 +524,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>86.84452287649546</v>
+        <v>90.61946902654867</v>
       </c>
       <c r="C5" t="n">
-        <v>85.42324646392339</v>
+        <v>90.23403699369415</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3250070607289672</v>
+        <v>0.2699704758066218</v>
       </c>
       <c r="E5" t="n">
-        <v>86.84452287649547</v>
+        <v>90.61946902654867</v>
       </c>
     </row>
     <row r="6">
@@ -542,16 +543,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>87.88181558664003</v>
+        <v>94.48377581120944</v>
       </c>
       <c r="C6" t="n">
-        <v>87.86995659813476</v>
+        <v>94.38819472779468</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3031642396003008</v>
+        <v>0.1538855811134757</v>
       </c>
       <c r="E6" t="n">
-        <v>87.88181558664003</v>
+        <v>94.48377581120944</v>
       </c>
     </row>
     <row r="7">
@@ -561,16 +562,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>87.64029100597756</v>
+        <v>92.15339233038348</v>
       </c>
       <c r="C7" t="n">
-        <v>87.23046812114239</v>
+        <v>92.07848796947664</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3275002591467152</v>
+        <v>0.1869601262083355</v>
       </c>
       <c r="E7" t="n">
-        <v>87.64029100597756</v>
+        <v>92.15339233038348</v>
       </c>
     </row>
     <row r="8">
@@ -580,16 +581,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>89.35120546025485</v>
+        <v>92.65486725663717</v>
       </c>
       <c r="C8" t="n">
-        <v>88.72567884377497</v>
+        <v>92.45776716282396</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2771090551064087</v>
+        <v>0.1630881650658011</v>
       </c>
       <c r="E8" t="n">
-        <v>89.35120546025485</v>
+        <v>92.65486725663717</v>
       </c>
     </row>
     <row r="9">
@@ -599,16 +600,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>94.95575221238938</v>
+        <v>95.66371681415929</v>
       </c>
       <c r="C9" t="n">
-        <v>94.88740816999957</v>
+        <v>95.59567236325566</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1227973622000718</v>
+        <v>0.1060918601230393</v>
       </c>
       <c r="E9" t="n">
-        <v>94.95575221238938</v>
+        <v>95.6637168141593</v>
       </c>
     </row>
     <row r="10">
@@ -618,16 +619,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>93.92330383480825</v>
+        <v>97.02064896755162</v>
       </c>
       <c r="C10" t="n">
-        <v>93.79676595459163</v>
+        <v>96.91094229712823</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1489421579362291</v>
+        <v>0.08152771384229709</v>
       </c>
       <c r="E10" t="n">
-        <v>93.92330383480825</v>
+        <v>97.02064896755162</v>
       </c>
     </row>
     <row r="11">
@@ -637,16 +638,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>88.06053685585515</v>
+        <v>95.42772861356931</v>
       </c>
       <c r="C11" t="n">
-        <v>88.07299793590153</v>
+        <v>95.38563761001724</v>
       </c>
       <c r="D11" t="n">
-        <v>0.28129397763405</v>
+        <v>0.1135901045175463</v>
       </c>
       <c r="E11" t="n">
-        <v>88.06053685585515</v>
+        <v>95.42772861356931</v>
       </c>
     </row>
     <row r="12">
@@ -656,16 +657,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>87.25732921565066</v>
+        <v>90.41297935103245</v>
       </c>
       <c r="C12" t="n">
-        <v>87.27963335223691</v>
+        <v>90.2243997079316</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3528201386817576</v>
+        <v>0.2901691132060175</v>
       </c>
       <c r="E12" t="n">
-        <v>87.25732921565066</v>
+        <v>90.41297935103245</v>
       </c>
     </row>
     <row r="13">
@@ -675,16 +676,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>90.8577063815431</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="C13" t="n">
-        <v>90.38575328519443</v>
+        <v>93.01852271392994</v>
       </c>
       <c r="D13" t="n">
-        <v>0.261331786448136</v>
+        <v>0.1874544579846164</v>
       </c>
       <c r="E13" t="n">
-        <v>90.8577063815431</v>
+        <v>93.33333333333334</v>
       </c>
     </row>
     <row r="14">
@@ -694,16 +695,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>87.28613569321534</v>
+        <v>89.43952802359881</v>
       </c>
       <c r="C14" t="n">
-        <v>86.27410642318685</v>
+        <v>87.73342149492933</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3257128099503461</v>
+        <v>0.3175051936806995</v>
       </c>
       <c r="E14" t="n">
-        <v>87.28613569321534</v>
+        <v>89.43952802359881</v>
       </c>
     </row>
     <row r="15">
@@ -713,16 +714,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>83.35876607929134</v>
+        <v>90.97362433931089</v>
       </c>
       <c r="C15" t="n">
-        <v>82.15081823493509</v>
+        <v>90.85080110896497</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5183553899871185</v>
+        <v>0.2330174217155824</v>
       </c>
       <c r="E15" t="n">
-        <v>83.35876607929134</v>
+        <v>90.97362433931089</v>
       </c>
     </row>
     <row r="16">
@@ -732,16 +733,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>86.60836166402824</v>
+        <v>89.5575221238938</v>
       </c>
       <c r="C16" t="n">
-        <v>86.0069477602373</v>
+        <v>89.06194223714945</v>
       </c>
       <c r="D16" t="n">
-        <v>0.38568416700388</v>
+        <v>0.2688846230002431</v>
       </c>
       <c r="E16" t="n">
-        <v>86.60836166402824</v>
+        <v>89.5575221238938</v>
       </c>
     </row>
     <row r="17">
@@ -751,16 +752,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>89.64601769911505</v>
+        <v>93.56932153392331</v>
       </c>
       <c r="C17" t="n">
-        <v>89.63772003972714</v>
+        <v>93.4233332237809</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2378654994291234</v>
+        <v>0.1698427266809934</v>
       </c>
       <c r="E17" t="n">
-        <v>89.64601769911505</v>
+        <v>93.5693215339233</v>
       </c>
     </row>
     <row r="18">
@@ -770,16 +771,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>82.14188704054533</v>
+        <v>92.36074706528603</v>
       </c>
       <c r="C18" t="n">
-        <v>81.63226598477776</v>
+        <v>91.86896178637683</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4348477874494468</v>
+        <v>0.2081771358920074</v>
       </c>
       <c r="E18" t="n">
-        <v>82.14188704054534</v>
+        <v>92.36074706528603</v>
       </c>
     </row>
     <row r="19">
@@ -789,16 +790,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>89.6482668535195</v>
+        <v>95.6637168141593</v>
       </c>
       <c r="C19" t="n">
-        <v>89.72908887974805</v>
+        <v>95.55630943788715</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2375954700061508</v>
+        <v>0.1317987839791385</v>
       </c>
       <c r="E19" t="n">
-        <v>89.64826685351949</v>
+        <v>95.6637168141593</v>
       </c>
     </row>
     <row r="20">
@@ -808,16 +809,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>88.05309734513274</v>
+        <v>89.2330383480826</v>
       </c>
       <c r="C20" t="n">
-        <v>87.44093345817701</v>
+        <v>87.9908308668897</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3818078119152536</v>
+        <v>0.3694274407923028</v>
       </c>
       <c r="E20" t="n">
-        <v>88.05309734513274</v>
+        <v>89.2330383480826</v>
       </c>
     </row>
     <row r="21">
@@ -827,16 +828,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>82.62554174344069</v>
+        <v>87.16814159292036</v>
       </c>
       <c r="C21" t="n">
-        <v>80.85325829689199</v>
+        <v>86.466299007271</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6392235482033963</v>
+        <v>0.3293061867560027</v>
       </c>
       <c r="E21" t="n">
-        <v>82.62554174344069</v>
+        <v>87.16814159292036</v>
       </c>
     </row>
     <row r="22">
@@ -846,16 +847,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>87.52679521449147</v>
+        <v>92.50737463126843</v>
       </c>
       <c r="C22" t="n">
-        <v>86.62144723498815</v>
+        <v>92.01000287541414</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4081130928359926</v>
+        <v>0.2288928982838115</v>
       </c>
       <c r="E22" t="n">
-        <v>87.52679521449147</v>
+        <v>92.50737463126843</v>
       </c>
     </row>
     <row r="23">
@@ -865,16 +866,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>82.71403731866192</v>
+        <v>89.79351032448378</v>
       </c>
       <c r="C23" t="n">
-        <v>81.97266122532523</v>
+        <v>89.26761280452001</v>
       </c>
       <c r="D23" t="n">
-        <v>0.534538891989117</v>
+        <v>0.3359085543609884</v>
       </c>
       <c r="E23" t="n">
-        <v>82.71403731866192</v>
+        <v>89.79351032448378</v>
       </c>
     </row>
     <row r="24">
@@ -884,16 +885,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>86.7551622418879</v>
+        <v>93.03834808259587</v>
       </c>
       <c r="C24" t="n">
-        <v>86.65534837341789</v>
+        <v>92.89158839882279</v>
       </c>
       <c r="D24" t="n">
-        <v>0.344184766151011</v>
+        <v>0.2145686666274438</v>
       </c>
       <c r="E24" t="n">
-        <v>86.7551622418879</v>
+        <v>93.03834808259587</v>
       </c>
     </row>
     <row r="25">
@@ -903,16 +904,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>87.16917966418394</v>
+        <v>90.3834808259587</v>
       </c>
       <c r="C25" t="n">
-        <v>85.98215881854399</v>
+        <v>90.12519343987756</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3779935009234274</v>
+        <v>0.3033928050722655</v>
       </c>
       <c r="E25" t="n">
-        <v>87.16917966418394</v>
+        <v>90.3834808259587</v>
       </c>
     </row>
     <row r="26">
@@ -922,16 +923,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>92.06489675516225</v>
+        <v>92.89085545722715</v>
       </c>
       <c r="C26" t="n">
-        <v>91.9429080416174</v>
+        <v>92.56501112165205</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2344091325573875</v>
+        <v>0.1899022967558267</v>
       </c>
       <c r="E26" t="n">
-        <v>92.06489675516225</v>
+        <v>92.89085545722715</v>
       </c>
     </row>
     <row r="27">
@@ -941,16 +942,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>83.39233038348083</v>
+        <v>83.53982300884955</v>
       </c>
       <c r="C27" t="n">
-        <v>83.32922317692743</v>
+        <v>82.80994878869402</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7788103495940353</v>
+        <v>0.7439825111481089</v>
       </c>
       <c r="E27" t="n">
-        <v>83.39233038348081</v>
+        <v>83.53982300884955</v>
       </c>
     </row>
     <row r="28">
@@ -960,16 +961,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>82.00589970501474</v>
+        <v>84.69026548672566</v>
       </c>
       <c r="C28" t="n">
-        <v>80.34323738072978</v>
+        <v>83.19001150424967</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5944358753974484</v>
+        <v>0.5555318374622099</v>
       </c>
       <c r="E28" t="n">
-        <v>82.00589970501474</v>
+        <v>84.69026548672566</v>
       </c>
     </row>
     <row r="29">
@@ -979,16 +980,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>91.85840707964601</v>
+        <v>98.61356932153392</v>
       </c>
       <c r="C29" t="n">
-        <v>91.72931198046672</v>
+        <v>98.61068472680604</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2346472997198968</v>
+        <v>0.05926988578042559</v>
       </c>
       <c r="E29" t="n">
-        <v>91.85840707964601</v>
+        <v>98.61356932153392</v>
       </c>
     </row>
     <row r="30">
@@ -998,16 +999,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>91.09144542772862</v>
+        <v>98.58407079646017</v>
       </c>
       <c r="C30" t="n">
-        <v>90.46424412526682</v>
+        <v>98.600646730116</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2233040218447665</v>
+        <v>0.04156410447474172</v>
       </c>
       <c r="E30" t="n">
-        <v>91.09144542772862</v>
+        <v>98.58407079646017</v>
       </c>
     </row>
     <row r="31">
@@ -1017,16 +1018,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>96.96165191740413</v>
+        <v>96.93215339233038</v>
       </c>
       <c r="C31" t="n">
-        <v>96.93113586829807</v>
+        <v>96.89154732831848</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1048462380889153</v>
+        <v>0.1000053139590667</v>
       </c>
       <c r="E31" t="n">
-        <v>96.96165191740413</v>
+        <v>96.93215339233038</v>
       </c>
     </row>
     <row r="32">
@@ -1036,16 +1037,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>87.8440211420514</v>
+        <v>91.97446921397821</v>
       </c>
       <c r="C32" t="n">
-        <v>87.2771713819279</v>
+        <v>91.53975062653986</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3554756721018632</v>
+        <v>0.2457394327184049</v>
       </c>
       <c r="E32" t="n">
-        <v>87.8440211420514</v>
+        <v>91.97446921397821</v>
       </c>
     </row>
     <row r="33">
@@ -1055,16 +1056,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.715150593951797</v>
+        <v>3.61288993211323</v>
       </c>
       <c r="C33" t="n">
-        <v>4.027234443011995</v>
+        <v>3.950481767131243</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1487006763310388</v>
+        <v>0.1442727903844741</v>
       </c>
       <c r="E33" t="n">
-        <v>3.715150593951797</v>
+        <v>3.61288993211323</v>
       </c>
     </row>
   </sheetData>
@@ -1078,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1110,16 +1111,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87.8440211420514</v>
+        <v>91.97446921397821</v>
       </c>
       <c r="B2" t="n">
-        <v>87.2771713819279</v>
+        <v>91.53975062653986</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3554756721018632</v>
+        <v>0.2457394327184049</v>
       </c>
       <c r="D2" t="n">
-        <v>87.8440211420514</v>
+        <v>91.97446921397821</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1129,16 +1130,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3.715150593951797</v>
+        <v>3.61288993211323</v>
       </c>
       <c r="B3" t="n">
-        <v>4.027234443011995</v>
+        <v>3.950481767131243</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1487006763310388</v>
+        <v>0.1442727903844741</v>
       </c>
       <c r="D3" t="n">
-        <v>3.715150593951797</v>
+        <v>3.61288993211323</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1148,16 +1149,16 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>81.83842132429058</v>
+        <v>87.65865621674928</v>
       </c>
       <c r="B4" t="n">
-        <v>81.24465382453145</v>
+        <v>87.19324525993083</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5080935251919547</v>
+        <v>0.3609405939802633</v>
       </c>
       <c r="D4" t="n">
-        <v>81.83842132429058</v>
+        <v>87.65865621674926</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1167,16 +1168,16 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5.503829275584718</v>
+        <v>4.317928299957321</v>
       </c>
       <c r="B5" t="n">
-        <v>5.697071981885062</v>
+        <v>4.587365317665403</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1713353167742858</v>
+        <v>0.167565926944197</v>
       </c>
       <c r="D5" t="n">
-        <v>5.503829275584718</v>
+        <v>4.317928299957321</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1186,16 +1187,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>64.56043449049444</v>
+        <v>81.97963650204586</v>
       </c>
       <c r="B6" t="n">
-        <v>63.35846266569646</v>
+        <v>81.26554291706898</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8602617637174101</v>
+        <v>0.5054986090294992</v>
       </c>
       <c r="D6" t="n">
-        <v>64.56043449049443</v>
+        <v>81.97963650204586</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1205,16 +1206,16 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7.86242047545445</v>
+        <v>5.31988168731759</v>
       </c>
       <c r="B7" t="n">
-        <v>8.232069377524395</v>
+        <v>5.683252021062777</v>
       </c>
       <c r="C7" t="n">
-        <v>0.19355431175789</v>
+        <v>0.194987510991812</v>
       </c>
       <c r="D7" t="n">
-        <v>7.862420475454449</v>
+        <v>5.319881687317591</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1224,16 +1225,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>91.80138236489937</v>
+        <v>65.12390822296616</v>
       </c>
       <c r="B8" t="n">
-        <v>91.34415628368239</v>
+        <v>64.00995050342915</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2517985150988956</v>
+        <v>0.8473526093772509</v>
       </c>
       <c r="D8" t="n">
-        <v>91.80138236489937</v>
+        <v>65.12390822296616</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1243,18 +1244,56 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3.520713838592158</v>
+        <v>8.154028567790915</v>
       </c>
       <c r="B9" t="n">
-        <v>3.857255239968123</v>
+        <v>8.668626105717335</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1415336286522811</v>
+        <v>0.1978767105001035</v>
       </c>
       <c r="D9" t="n">
-        <v>3.520713838592159</v>
+        <v>8.154028567790915</v>
       </c>
       <c r="E9" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>52.44438965734997</v>
+      </c>
+      <c r="B10" t="n">
+        <v>49.4510723472042</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.131155228759938</v>
+      </c>
+      <c r="D10" t="n">
+        <v>52.44438965734997</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9.209824499574564</v>
+      </c>
+      <c r="B11" t="n">
+        <v>10.29354281843498</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.2338060840685769</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.209824499574564</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Std</t>
         </is>
@@ -1308,16 +1347,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.77890812204258</v>
+        <v>82.27138643067846</v>
       </c>
       <c r="C2" t="n">
-        <v>81.80677436593641</v>
+        <v>82.44476115383739</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4437605415082847</v>
+        <v>0.4580048098028177</v>
       </c>
       <c r="E2" t="n">
-        <v>81.77890812204258</v>
+        <v>82.27138643067846</v>
       </c>
     </row>
     <row r="3">
@@ -1327,16 +1366,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78.93156515194768</v>
+        <v>86.84383082898641</v>
       </c>
       <c r="C3" t="n">
-        <v>78.97629519305951</v>
+        <v>86.01502101366042</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6387586455171307</v>
+        <v>0.3896006838069297</v>
       </c>
       <c r="E3" t="n">
-        <v>78.93156515194768</v>
+        <v>86.84383082898641</v>
       </c>
     </row>
     <row r="4">
@@ -1346,16 +1385,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>81.63106947291932</v>
+        <v>84.36578171091445</v>
       </c>
       <c r="C4" t="n">
-        <v>80.84442779420331</v>
+        <v>83.95454335704657</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5407692650216631</v>
+        <v>0.4894321668175204</v>
       </c>
       <c r="E4" t="n">
-        <v>81.63106947291931</v>
+        <v>84.36578171091445</v>
       </c>
     </row>
     <row r="5">
@@ -1365,16 +1404,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>77.45975311205113</v>
+        <v>85.23507988823432</v>
       </c>
       <c r="C5" t="n">
-        <v>77.40419027442061</v>
+        <v>84.37411946832444</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5083728658190618</v>
+        <v>0.355641016868564</v>
       </c>
       <c r="E5" t="n">
-        <v>77.45975311205115</v>
+        <v>85.23507988823432</v>
       </c>
     </row>
     <row r="6">
@@ -1384,16 +1423,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>80.89775863113002</v>
+        <v>88.28943156947724</v>
       </c>
       <c r="C6" t="n">
-        <v>79.61519124298975</v>
+        <v>88.3674388894253</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5105313768687968</v>
+        <v>0.2935437642969191</v>
       </c>
       <c r="E6" t="n">
-        <v>80.89775863113002</v>
+        <v>88.28943156947724</v>
       </c>
     </row>
     <row r="7">
@@ -1403,16 +1442,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>81.21307277744617</v>
+        <v>89.43952802359881</v>
       </c>
       <c r="C7" t="n">
-        <v>79.69236205691561</v>
+        <v>89.22903831771394</v>
       </c>
       <c r="D7" t="n">
-        <v>0.467518546183904</v>
+        <v>0.2652905034832657</v>
       </c>
       <c r="E7" t="n">
-        <v>81.21307277744617</v>
+        <v>89.43952802359881</v>
       </c>
     </row>
     <row r="8">
@@ -1422,16 +1461,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83.27779652073114</v>
+        <v>90.05917006202476</v>
       </c>
       <c r="C8" t="n">
-        <v>82.97636637072705</v>
+        <v>89.73102154856511</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4483930509537458</v>
+        <v>0.2333400314999684</v>
       </c>
       <c r="E8" t="n">
-        <v>83.27779652073114</v>
+        <v>90.05917006202476</v>
       </c>
     </row>
     <row r="9">
@@ -1441,16 +1480,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>89.26547807506985</v>
+        <v>92.47787610619469</v>
       </c>
       <c r="C9" t="n">
-        <v>89.14301024029025</v>
+        <v>91.97041936096899</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2750617443273465</v>
+        <v>0.1893304443532543</v>
       </c>
       <c r="E9" t="n">
-        <v>89.26547807506986</v>
+        <v>92.47787610619469</v>
       </c>
     </row>
     <row r="10">
@@ -1460,16 +1499,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>84.31197501708492</v>
+        <v>93.68731563421829</v>
       </c>
       <c r="C10" t="n">
-        <v>84.0507671572406</v>
+        <v>93.4608237467761</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4350238217972219</v>
+        <v>0.1592718335664055</v>
       </c>
       <c r="E10" t="n">
-        <v>84.31197501708492</v>
+        <v>93.68731563421828</v>
       </c>
     </row>
     <row r="11">
@@ -1479,16 +1518,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>82.07190373619149</v>
+        <v>89.91150442477877</v>
       </c>
       <c r="C11" t="n">
-        <v>81.62637281518836</v>
+        <v>89.81130656875303</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5849634101924797</v>
+        <v>0.2542722464810746</v>
       </c>
       <c r="E11" t="n">
-        <v>82.07190373619149</v>
+        <v>89.91150442477877</v>
       </c>
     </row>
     <row r="12">
@@ -1498,16 +1537,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>84.10064100900527</v>
+        <v>87.69911504424779</v>
       </c>
       <c r="C12" t="n">
-        <v>82.81326628572536</v>
+        <v>87.2360821671721</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5203831361761938</v>
+        <v>0.3443835477519315</v>
       </c>
       <c r="E12" t="n">
-        <v>84.10064100900527</v>
+        <v>87.69911504424779</v>
       </c>
     </row>
     <row r="13">
@@ -1517,16 +1556,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>80.67422728570315</v>
+        <v>89.79351032448378</v>
       </c>
       <c r="C13" t="n">
-        <v>79.91537816101294</v>
+        <v>89.02593268446478</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5312523586365084</v>
+        <v>0.296459076802906</v>
       </c>
       <c r="E13" t="n">
-        <v>80.67422728570315</v>
+        <v>89.79351032448378</v>
       </c>
     </row>
     <row r="14">
@@ -1536,16 +1575,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>84.80981669391603</v>
+        <v>85.28040900007787</v>
       </c>
       <c r="C14" t="n">
-        <v>84.02900055269406</v>
+        <v>83.82607196535828</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4193099545547739</v>
+        <v>0.4064942386641633</v>
       </c>
       <c r="E14" t="n">
-        <v>84.80981669391603</v>
+        <v>85.28040900007785</v>
       </c>
     </row>
     <row r="15">
@@ -1555,16 +1594,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>80.63486708362529</v>
+        <v>83.56300660040311</v>
       </c>
       <c r="C15" t="n">
-        <v>80.38061200380534</v>
+        <v>83.33031275249937</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5076447090134024</v>
+        <v>0.4750356876140965</v>
       </c>
       <c r="E15" t="n">
-        <v>80.63486708362529</v>
+        <v>83.56300660040311</v>
       </c>
     </row>
     <row r="16">
@@ -1574,16 +1613,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>79.57292018097043</v>
+        <v>87.93510324483776</v>
       </c>
       <c r="C16" t="n">
-        <v>78.96058518381608</v>
+        <v>87.3547673291404</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5537055654451251</v>
+        <v>0.3429434563149698</v>
       </c>
       <c r="E16" t="n">
-        <v>79.57292018097041</v>
+        <v>87.93510324483776</v>
       </c>
     </row>
     <row r="17">
@@ -1593,16 +1632,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>84.40133565169249</v>
+        <v>91.12094395280236</v>
       </c>
       <c r="C17" t="n">
-        <v>84.25309966966874</v>
+        <v>91.13252683649851</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4053716144214074</v>
+        <v>0.2378949016559394</v>
       </c>
       <c r="E17" t="n">
-        <v>84.40133565169249</v>
+        <v>91.12094395280236</v>
       </c>
     </row>
     <row r="18">
@@ -1612,16 +1651,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>76.03119404147094</v>
+        <v>83.985069074992</v>
       </c>
       <c r="C18" t="n">
-        <v>75.42264971665924</v>
+        <v>83.91638278276612</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6002242468452702</v>
+        <v>0.4313012138164291</v>
       </c>
       <c r="E18" t="n">
-        <v>76.03119404147094</v>
+        <v>83.985069074992</v>
       </c>
     </row>
     <row r="19">
@@ -1631,16 +1670,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>88.05776866581891</v>
+        <v>90.85614927464771</v>
       </c>
       <c r="C19" t="n">
-        <v>88.12215516321753</v>
+        <v>90.95332308134431</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3095063509603885</v>
+        <v>0.2078685977345837</v>
       </c>
       <c r="E19" t="n">
-        <v>88.05776866581891</v>
+        <v>90.85614927464771</v>
       </c>
     </row>
     <row r="20">
@@ -1650,16 +1689,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>73.53523819410202</v>
+        <v>89.08554572271387</v>
       </c>
       <c r="C20" t="n">
-        <v>72.84191615575676</v>
+        <v>88.14946403945892</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7066012476726125</v>
+        <v>0.3597370643595544</v>
       </c>
       <c r="E20" t="n">
-        <v>73.53523819410202</v>
+        <v>89.08554572271387</v>
       </c>
     </row>
     <row r="21">
@@ -1669,16 +1708,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>69.00509519978547</v>
+        <v>77.52437304820975</v>
       </c>
       <c r="C21" t="n">
-        <v>67.40112695101622</v>
+        <v>75.7698932796207</v>
       </c>
       <c r="D21" t="n">
-        <v>0.922631406178698</v>
+        <v>0.806225572557499</v>
       </c>
       <c r="E21" t="n">
-        <v>69.00509519978547</v>
+        <v>77.52437304820975</v>
       </c>
     </row>
     <row r="22">
@@ -1688,16 +1727,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>81.68885543992594</v>
+        <v>89.38347217536484</v>
       </c>
       <c r="C22" t="n">
-        <v>80.10862780366101</v>
+        <v>88.50384722624548</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6377211284435664</v>
+        <v>0.3867631372141963</v>
       </c>
       <c r="E22" t="n">
-        <v>81.68885543992594</v>
+        <v>89.38347217536484</v>
       </c>
     </row>
     <row r="23">
@@ -1707,16 +1746,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>75.72790422062475</v>
+        <v>80.74213444752982</v>
       </c>
       <c r="C23" t="n">
-        <v>75.3590506515017</v>
+        <v>79.47178168814706</v>
       </c>
       <c r="D23" t="n">
-        <v>0.619099364678065</v>
+        <v>0.7053214968026926</v>
       </c>
       <c r="E23" t="n">
-        <v>75.72790422062475</v>
+        <v>80.74213444752982</v>
       </c>
     </row>
     <row r="24">
@@ -1726,16 +1765,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>81.42475280928036</v>
+        <v>84.24778761061947</v>
       </c>
       <c r="C24" t="n">
-        <v>80.97938206014702</v>
+        <v>83.82133398512973</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5060286498007674</v>
+        <v>0.4212806468169826</v>
       </c>
       <c r="E24" t="n">
-        <v>81.42475280928036</v>
+        <v>84.24778761061947</v>
       </c>
     </row>
     <row r="25">
@@ -1745,16 +1784,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>82.8910284691044</v>
+        <v>85.19485462677012</v>
       </c>
       <c r="C25" t="n">
-        <v>81.95533170800238</v>
+        <v>84.59551076823659</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5071898053128583</v>
+        <v>0.4019781112748508</v>
       </c>
       <c r="E25" t="n">
-        <v>82.8910284691044</v>
+        <v>85.19485462677014</v>
       </c>
     </row>
     <row r="26">
@@ -1764,16 +1803,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>84.10427425842784</v>
+        <v>91.44542772861357</v>
       </c>
       <c r="C26" t="n">
-        <v>83.79522490135159</v>
+        <v>91.40389304516704</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4093482368412272</v>
+        <v>0.2208344100370596</v>
       </c>
       <c r="E26" t="n">
-        <v>84.10427425842784</v>
+        <v>91.44542772861357</v>
       </c>
     </row>
     <row r="27">
@@ -1783,16 +1822,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>74.22365245374094</v>
+        <v>82.86135693215338</v>
       </c>
       <c r="C27" t="n">
-        <v>73.65796942584348</v>
+        <v>82.41236270660326</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9079017833108083</v>
+        <v>0.7207907706489398</v>
       </c>
       <c r="E27" t="n">
-        <v>74.22365245374095</v>
+        <v>82.86135693215338</v>
       </c>
     </row>
     <row r="28">
@@ -1802,16 +1841,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>77.1759271273973</v>
+        <v>83.09734513274336</v>
       </c>
       <c r="C28" t="n">
-        <v>76.1474052653631</v>
+        <v>82.29061454011476</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6738221229131643</v>
+        <v>0.5319223459994343</v>
       </c>
       <c r="E28" t="n">
-        <v>77.17592712739729</v>
+        <v>83.09734513274336</v>
       </c>
     </row>
     <row r="29">
@@ -1821,16 +1860,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>89.58702064896755</v>
+        <v>93.39233038348083</v>
       </c>
       <c r="C29" t="n">
-        <v>89.48957928926305</v>
+        <v>93.39305737808635</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2734412079056104</v>
+        <v>0.1869806041392925</v>
       </c>
       <c r="E29" t="n">
-        <v>89.58702064896755</v>
+        <v>93.39233038348083</v>
       </c>
     </row>
     <row r="30">
@@ -1840,16 +1879,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>89.20353982300885</v>
+        <v>93.48082595870207</v>
       </c>
       <c r="C30" t="n">
-        <v>88.12221090723219</v>
+        <v>93.43053712939096</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2956626599420208</v>
+        <v>0.1486760050318783</v>
       </c>
       <c r="E30" t="n">
-        <v>89.20353982300885</v>
+        <v>93.48082595870207</v>
       </c>
     </row>
     <row r="31">
@@ -1859,16 +1898,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>97.46329985553508</v>
+        <v>96.49002153997871</v>
       </c>
       <c r="C31" t="n">
-        <v>97.44928536923439</v>
+        <v>96.42116898740908</v>
       </c>
       <c r="D31" t="n">
-        <v>0.08280693851653874</v>
+        <v>0.1075994331937788</v>
       </c>
       <c r="E31" t="n">
-        <v>97.46329985553508</v>
+        <v>96.49002153997871</v>
       </c>
     </row>
     <row r="32">
@@ -1878,16 +1917,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>81.83842132429058</v>
+        <v>87.65865621674928</v>
       </c>
       <c r="C32" t="n">
-        <v>81.24465382453145</v>
+        <v>87.19324525993083</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5080935251919547</v>
+        <v>0.3609405939802633</v>
       </c>
       <c r="E32" t="n">
-        <v>81.83842132429058</v>
+        <v>87.65865621674926</v>
       </c>
     </row>
     <row r="33">
@@ -1897,16 +1936,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5.503829275584718</v>
+        <v>4.317928299957321</v>
       </c>
       <c r="C33" t="n">
-        <v>5.697071981885062</v>
+        <v>4.587365317665403</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1713353167742858</v>
+        <v>0.167565926944197</v>
       </c>
       <c r="E33" t="n">
-        <v>5.503829275584718</v>
+        <v>4.317928299957321</v>
       </c>
     </row>
   </sheetData>
@@ -1957,16 +1996,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>62.90409086583794</v>
+        <v>79.77024022699159</v>
       </c>
       <c r="C2" t="n">
-        <v>61.81794881343617</v>
+        <v>78.40963030148934</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8611909687519074</v>
+        <v>0.5257910272106529</v>
       </c>
       <c r="E2" t="n">
-        <v>62.90409086583794</v>
+        <v>79.77024022699158</v>
       </c>
     </row>
     <row r="3">
@@ -1976,16 +2015,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55.07893666900232</v>
+        <v>82.395608958555</v>
       </c>
       <c r="C3" t="n">
-        <v>53.17380682144509</v>
+        <v>81.85550491783742</v>
       </c>
       <c r="D3" t="n">
-        <v>1.093226370712121</v>
+        <v>0.4720271174640705</v>
       </c>
       <c r="E3" t="n">
-        <v>55.07893666900232</v>
+        <v>82.395608958555</v>
       </c>
     </row>
     <row r="4">
@@ -1995,16 +2034,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>71.06064931357538</v>
+        <v>81.86411647159578</v>
       </c>
       <c r="C4" t="n">
-        <v>70.47675280702566</v>
+        <v>81.13747166773824</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6728587831060092</v>
+        <v>0.539342588732446</v>
       </c>
       <c r="E4" t="n">
-        <v>71.06064931357538</v>
+        <v>81.86411647159578</v>
       </c>
     </row>
     <row r="5">
@@ -2014,16 +2053,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.32572081073365</v>
+        <v>82.60002249154404</v>
       </c>
       <c r="C5" t="n">
-        <v>60.87105005634946</v>
+        <v>81.28013082420159</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7545674746235211</v>
+        <v>0.4305147267878056</v>
       </c>
       <c r="E5" t="n">
-        <v>63.32572081073365</v>
+        <v>82.60002249154404</v>
       </c>
     </row>
     <row r="6">
@@ -2033,16 +2072,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65.23793458420921</v>
+        <v>80.38659503974948</v>
       </c>
       <c r="C6" t="n">
-        <v>63.8571032030238</v>
+        <v>78.74365884033827</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8013505324721336</v>
+        <v>0.5088963020592928</v>
       </c>
       <c r="E6" t="n">
-        <v>65.2379345842092</v>
+        <v>80.38659503974948</v>
       </c>
     </row>
     <row r="7">
@@ -2052,16 +2091,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>49.50267735880068</v>
+        <v>83.95366741926833</v>
       </c>
       <c r="C7" t="n">
-        <v>47.57814569652296</v>
+        <v>83.44933268191163</v>
       </c>
       <c r="D7" t="n">
-        <v>1.107857163747152</v>
+        <v>0.4282560899232825</v>
       </c>
       <c r="E7" t="n">
-        <v>49.50267735880068</v>
+        <v>83.95366741926833</v>
       </c>
     </row>
     <row r="8">
@@ -2071,16 +2110,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>67.70421889462712</v>
+        <v>77.58804141904342</v>
       </c>
       <c r="C8" t="n">
-        <v>66.15657683603689</v>
+        <v>76.11177735754455</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8429005611532678</v>
+        <v>0.6469644040807907</v>
       </c>
       <c r="E8" t="n">
-        <v>67.70421889462712</v>
+        <v>77.58804141904342</v>
       </c>
     </row>
     <row r="9">
@@ -2090,16 +2129,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>64.6111990588154</v>
+        <v>87.47022033062569</v>
       </c>
       <c r="C9" t="n">
-        <v>64.08693784404502</v>
+        <v>86.94199900553443</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8700907851879796</v>
+        <v>0.3470593688568139</v>
       </c>
       <c r="E9" t="n">
-        <v>64.61119905881539</v>
+        <v>87.47022033062569</v>
       </c>
     </row>
     <row r="10">
@@ -2109,16 +2148,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>71.17310703379788</v>
+        <v>87.05066652825717</v>
       </c>
       <c r="C10" t="n">
-        <v>71.33463719855234</v>
+        <v>86.49585815128196</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6745136694361766</v>
+        <v>0.3176183146861149</v>
       </c>
       <c r="E10" t="n">
-        <v>71.17310703379788</v>
+        <v>87.05066652825717</v>
       </c>
     </row>
     <row r="11">
@@ -2128,16 +2167,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>60.55908788138306</v>
+        <v>88.61824064222009</v>
       </c>
       <c r="C11" t="n">
-        <v>60.0157320540347</v>
+        <v>88.55478780103178</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9095094551642735</v>
+        <v>0.2736783500760794</v>
       </c>
       <c r="E11" t="n">
-        <v>60.55908788138306</v>
+        <v>88.61824064222009</v>
       </c>
     </row>
     <row r="12">
@@ -2147,16 +2186,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>64.12763086185866</v>
+        <v>82.10460298099466</v>
       </c>
       <c r="C12" t="n">
-        <v>63.77312648148116</v>
+        <v>82.06200711125676</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8097013731797537</v>
+        <v>0.5129101977994044</v>
       </c>
       <c r="E12" t="n">
-        <v>64.12763086185866</v>
+        <v>82.10460298099466</v>
       </c>
     </row>
     <row r="13">
@@ -2166,16 +2205,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>67.94799262969403</v>
+        <v>83.86897810534694</v>
       </c>
       <c r="C13" t="n">
-        <v>67.39448154118523</v>
+        <v>83.72729147940831</v>
       </c>
       <c r="D13" t="n">
-        <v>0.813200189669927</v>
+        <v>0.4601940857013688</v>
       </c>
       <c r="E13" t="n">
-        <v>67.94799262969403</v>
+        <v>83.86897810534694</v>
       </c>
     </row>
     <row r="14">
@@ -2185,16 +2224,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>67.69591432451838</v>
+        <v>81.47907853874167</v>
       </c>
       <c r="C14" t="n">
-        <v>65.53415282966903</v>
+        <v>80.84544218715604</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8474355661620697</v>
+        <v>0.4915499498485588</v>
       </c>
       <c r="E14" t="n">
-        <v>67.69591432451838</v>
+        <v>81.47907853874169</v>
       </c>
     </row>
     <row r="15">
@@ -2204,16 +2243,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>58.34029706139327</v>
+        <v>80.92743016808103</v>
       </c>
       <c r="C15" t="n">
-        <v>56.02483681547125</v>
+        <v>80.64636046154173</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9763530910015106</v>
+        <v>0.4607103577038895</v>
       </c>
       <c r="E15" t="n">
-        <v>58.34029706139327</v>
+        <v>80.92743016808103</v>
       </c>
     </row>
     <row r="16">
@@ -2223,16 +2262,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>50.78677151186429</v>
+        <v>78.7868407166152</v>
       </c>
       <c r="C16" t="n">
-        <v>50.07745515766497</v>
+        <v>78.05544250883031</v>
       </c>
       <c r="D16" t="n">
-        <v>1.10258673230807</v>
+        <v>0.5980326567466061</v>
       </c>
       <c r="E16" t="n">
-        <v>50.78677151186429</v>
+        <v>78.7868407166152</v>
       </c>
     </row>
     <row r="17">
@@ -2242,16 +2281,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>64.93464476336301</v>
+        <v>86.96182492928139</v>
       </c>
       <c r="C17" t="n">
-        <v>63.65473292181065</v>
+        <v>86.80573364736236</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9038064749600986</v>
+        <v>0.3198507550347131</v>
       </c>
       <c r="E17" t="n">
-        <v>64.93464476336301</v>
+        <v>86.96182492928139</v>
       </c>
     </row>
     <row r="18">
@@ -2261,16 +2300,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>62.49266862170087</v>
+        <v>75.12452529866175</v>
       </c>
       <c r="C18" t="n">
-        <v>60.23325865229716</v>
+        <v>75.06170467601672</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8954438753426075</v>
+        <v>0.5995997079958518</v>
       </c>
       <c r="E18" t="n">
-        <v>62.49266862170089</v>
+        <v>75.12452529866175</v>
       </c>
     </row>
     <row r="19">
@@ -2280,16 +2319,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>74.62495350305798</v>
+        <v>86.16795993044923</v>
       </c>
       <c r="C19" t="n">
-        <v>74.23648937606764</v>
+        <v>86.23988691770539</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6250616657237212</v>
+        <v>0.3716908313489209</v>
       </c>
       <c r="E19" t="n">
-        <v>74.62495350305798</v>
+        <v>86.16795993044923</v>
       </c>
     </row>
     <row r="20">
@@ -2299,16 +2338,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>59.50743518542548</v>
+        <v>77.7729911158401</v>
       </c>
       <c r="C20" t="n">
-        <v>56.71225384012689</v>
+        <v>77.19537350837393</v>
       </c>
       <c r="D20" t="n">
-        <v>1.041958554089069</v>
+        <v>0.6513229863756957</v>
       </c>
       <c r="E20" t="n">
-        <v>59.50743518542548</v>
+        <v>77.7729911158401</v>
       </c>
     </row>
     <row r="21">
@@ -2318,16 +2357,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>57.77013641986523</v>
+        <v>69.02075277467797</v>
       </c>
       <c r="C21" t="n">
-        <v>54.43911899729596</v>
+        <v>67.20103504869232</v>
       </c>
       <c r="D21" t="n">
-        <v>1.106302042553822</v>
+        <v>1.034559998572028</v>
       </c>
       <c r="E21" t="n">
-        <v>57.77013641986523</v>
+        <v>69.02075277467797</v>
       </c>
     </row>
     <row r="22">
@@ -2337,16 +2376,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>66.14564139828198</v>
+        <v>81.02440332528828</v>
       </c>
       <c r="C22" t="n">
-        <v>65.29294476773937</v>
+        <v>79.55552652721749</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8011704723040263</v>
+        <v>0.6936149259369511</v>
       </c>
       <c r="E22" t="n">
-        <v>66.14564139828198</v>
+        <v>81.02440332528828</v>
       </c>
     </row>
     <row r="23">
@@ -2356,16 +2395,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>60.04671320686166</v>
+        <v>77.37861054161368</v>
       </c>
       <c r="C23" t="n">
-        <v>58.22819080861878</v>
+        <v>77.01391829510132</v>
       </c>
       <c r="D23" t="n">
-        <v>0.99059978723526</v>
+        <v>0.5828866411621372</v>
       </c>
       <c r="E23" t="n">
-        <v>60.04671320686165</v>
+        <v>77.37861054161368</v>
       </c>
     </row>
     <row r="24">
@@ -2375,16 +2414,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>62.69535203591727</v>
+        <v>80.24429277069871</v>
       </c>
       <c r="C24" t="n">
-        <v>61.78005594170787</v>
+        <v>79.77764068122178</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9045313368240991</v>
+        <v>0.5040460065783312</v>
       </c>
       <c r="E24" t="n">
-        <v>62.69535203591727</v>
+        <v>80.24429277069871</v>
       </c>
     </row>
     <row r="25">
@@ -2394,16 +2433,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>59.56937343748648</v>
+        <v>79.79506743137917</v>
       </c>
       <c r="C25" t="n">
-        <v>58.71431919979183</v>
+        <v>79.03315292786728</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9839524954557419</v>
+        <v>0.5287019353359937</v>
       </c>
       <c r="E25" t="n">
-        <v>59.56937343748648</v>
+        <v>79.79506743137917</v>
       </c>
     </row>
     <row r="26">
@@ -2413,16 +2452,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>67.90897845137069</v>
+        <v>80.00328722566805</v>
       </c>
       <c r="C26" t="n">
-        <v>66.84253259485942</v>
+        <v>79.38564717960296</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8044209193438292</v>
+        <v>0.5320528188017002</v>
       </c>
       <c r="E26" t="n">
-        <v>67.90897845137069</v>
+        <v>80.00328722566805</v>
       </c>
     </row>
     <row r="27">
@@ -2432,16 +2471,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>57.90050086938469</v>
+        <v>74.95713630740751</v>
       </c>
       <c r="C27" t="n">
-        <v>58.64240278467916</v>
+        <v>72.70725685555796</v>
       </c>
       <c r="D27" t="n">
-        <v>1.248344767124703</v>
+        <v>1.013957747948977</v>
       </c>
       <c r="E27" t="n">
-        <v>57.90050086938469</v>
+        <v>74.95713630740751</v>
       </c>
     </row>
     <row r="28">
@@ -2451,16 +2490,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>62.01532885232571</v>
+        <v>76.64183946227908</v>
       </c>
       <c r="C28" t="n">
-        <v>60.78489589874825</v>
+        <v>75.25655055545501</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9062902592122555</v>
+        <v>0.693461561249569</v>
       </c>
       <c r="E28" t="n">
-        <v>62.01532885232572</v>
+        <v>76.64183946227908</v>
       </c>
     </row>
     <row r="29">
@@ -2470,16 +2509,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>73.32615334042683</v>
+        <v>89.5575221238938</v>
       </c>
       <c r="C29" t="n">
-        <v>72.04919599592736</v>
+        <v>89.51526308781499</v>
       </c>
       <c r="D29" t="n">
-        <v>0.7013125476737817</v>
+        <v>0.2646358555629074</v>
       </c>
       <c r="E29" t="n">
-        <v>73.32615334042683</v>
+        <v>89.5575221238938</v>
       </c>
     </row>
     <row r="30">
@@ -2489,16 +2528,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>78.66002301057968</v>
+        <v>89.88252493533682</v>
       </c>
       <c r="C30" t="n">
-        <v>78.31249068543744</v>
+        <v>88.92550499227461</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4470778661081568</v>
+        <v>0.2552775093675488</v>
       </c>
       <c r="E30" t="n">
-        <v>78.66002301057968</v>
+        <v>89.88252493533682</v>
       </c>
     </row>
     <row r="31">
@@ -2508,16 +2547,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>89.15890275867437</v>
+        <v>95.99200685127035</v>
       </c>
       <c r="C31" t="n">
-        <v>88.65825334984179</v>
+        <v>95.97539731470329</v>
       </c>
       <c r="D31" t="n">
-        <v>0.310237130895257</v>
+        <v>0.1057534519364708</v>
       </c>
       <c r="E31" t="n">
-        <v>89.15890275867437</v>
+        <v>95.99200685127035</v>
       </c>
     </row>
     <row r="32">
@@ -2527,16 +2566,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>64.56043449049444</v>
+        <v>81.97963650204586</v>
       </c>
       <c r="C32" t="n">
-        <v>63.35846266569646</v>
+        <v>81.26554291706898</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8602617637174101</v>
+        <v>0.5054986090294992</v>
       </c>
       <c r="E32" t="n">
-        <v>64.56043449049443</v>
+        <v>81.97963650204586</v>
       </c>
     </row>
     <row r="33">
@@ -2546,16 +2585,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7.86242047545445</v>
+        <v>5.31988168731759</v>
       </c>
       <c r="C33" t="n">
-        <v>8.232069377524395</v>
+        <v>5.683252021062777</v>
       </c>
       <c r="D33" t="n">
-        <v>0.19355431175789</v>
+        <v>0.194987510991812</v>
       </c>
       <c r="E33" t="n">
-        <v>7.862420475454449</v>
+        <v>5.319881687317591</v>
       </c>
     </row>
   </sheetData>
@@ -2606,16 +2645,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>88.23008849557523</v>
+        <v>63.42883588958382</v>
       </c>
       <c r="C2" t="n">
-        <v>87.31970192682398</v>
+        <v>62.9817857459207</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3791622403555569</v>
+        <v>0.8083207135399182</v>
       </c>
       <c r="E2" t="n">
-        <v>88.23008849557522</v>
+        <v>63.42883588958382</v>
       </c>
     </row>
     <row r="3">
@@ -2625,16 +2664,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>91.50442477876106</v>
+        <v>56.02254344760767</v>
       </c>
       <c r="C3" t="n">
-        <v>91.34096629094032</v>
+        <v>54.07067207848587</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2432806223577548</v>
+        <v>1.028946647544702</v>
       </c>
       <c r="E3" t="n">
-        <v>91.50442477876106</v>
+        <v>56.02254344760767</v>
       </c>
     </row>
     <row r="4">
@@ -2644,16 +2683,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>88.40707964601771</v>
+        <v>72.71325876521423</v>
       </c>
       <c r="C4" t="n">
-        <v>87.3363145917052</v>
+        <v>72.79685750906354</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3879015704675112</v>
+        <v>0.6538229351242383</v>
       </c>
       <c r="E4" t="n">
-        <v>88.40707964601771</v>
+        <v>72.71325876521423</v>
       </c>
     </row>
     <row r="5">
@@ -2663,16 +2702,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>89.49852507374632</v>
+        <v>63.50219292554434</v>
       </c>
       <c r="C5" t="n">
-        <v>89.49972354998032</v>
+        <v>60.20053193368532</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2587755422612342</v>
+        <v>0.8335192675391833</v>
       </c>
       <c r="E5" t="n">
-        <v>89.49852507374632</v>
+        <v>63.50219292554434</v>
       </c>
     </row>
     <row r="6">
@@ -2682,16 +2721,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>95.36873156342183</v>
+        <v>63.02900544122353</v>
       </c>
       <c r="C6" t="n">
-        <v>95.32510763702926</v>
+        <v>60.58037728505222</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1284950972457106</v>
+        <v>0.8224633648991585</v>
       </c>
       <c r="E6" t="n">
-        <v>95.36873156342183</v>
+        <v>63.02900544122353</v>
       </c>
     </row>
     <row r="7">
@@ -2701,16 +2740,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>90.53097345132744</v>
+        <v>50.74317251879341</v>
       </c>
       <c r="C7" t="n">
-        <v>90.19659744341917</v>
+        <v>50.04476694320059</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2291742112545762</v>
+        <v>1.08183423380057</v>
       </c>
       <c r="E7" t="n">
-        <v>90.53097345132744</v>
+        <v>50.74317251879341</v>
       </c>
     </row>
     <row r="8">
@@ -2720,16 +2759,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>93.21533923303835</v>
+        <v>69.06045900051039</v>
       </c>
       <c r="C8" t="n">
-        <v>93.0379527298673</v>
+        <v>68.83677551327423</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1680777623893846</v>
+        <v>0.7780060096178204</v>
       </c>
       <c r="E8" t="n">
-        <v>93.21533923303835</v>
+        <v>69.06045900051038</v>
       </c>
     </row>
     <row r="9">
@@ -2739,16 +2778,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>96.16519174041298</v>
+        <v>65.85204024256265</v>
       </c>
       <c r="C9" t="n">
-        <v>96.11139678591412</v>
+        <v>65.32055308852178</v>
       </c>
       <c r="D9" t="n">
-        <v>0.10203844572452</v>
+        <v>0.8495052624493837</v>
       </c>
       <c r="E9" t="n">
-        <v>96.16519174041298</v>
+        <v>65.85204024256265</v>
       </c>
     </row>
     <row r="10">
@@ -2758,16 +2797,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>96.46017699115043</v>
+        <v>71.94249085199699</v>
       </c>
       <c r="C10" t="n">
-        <v>96.24300815833857</v>
+        <v>71.76871847814301</v>
       </c>
       <c r="D10" t="n">
-        <v>0.09699079194281997</v>
+        <v>0.6667305268347263</v>
       </c>
       <c r="E10" t="n">
-        <v>96.46017699115045</v>
+        <v>71.94249085199699</v>
       </c>
     </row>
     <row r="11">
@@ -2777,16 +2816,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>93.42182890855457</v>
+        <v>62.17320219033037</v>
       </c>
       <c r="C11" t="n">
-        <v>93.12227284553553</v>
+        <v>62.22353813150429</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1551010521051163</v>
+        <v>0.8801199237505595</v>
       </c>
       <c r="E11" t="n">
-        <v>93.42182890855457</v>
+        <v>62.17320219033037</v>
       </c>
     </row>
     <row r="12">
@@ -2796,16 +2835,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>90.64896755162242</v>
+        <v>65.39641346378428</v>
       </c>
       <c r="C12" t="n">
-        <v>90.15753408033757</v>
+        <v>64.94059045516309</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2914907947056539</v>
+        <v>0.781718463699023</v>
       </c>
       <c r="E12" t="n">
-        <v>90.64896755162242</v>
+        <v>65.39641346378428</v>
       </c>
     </row>
     <row r="13">
@@ -2815,16 +2854,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>93.59882005899705</v>
+        <v>67.38717462953832</v>
       </c>
       <c r="C13" t="n">
-        <v>93.47011011178012</v>
+        <v>66.80471374292367</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1633676926513241</v>
+        <v>0.8117480133970579</v>
       </c>
       <c r="E13" t="n">
-        <v>93.59882005899706</v>
+        <v>67.38717462953831</v>
       </c>
     </row>
     <row r="14">
@@ -2834,16 +2873,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>89.64601769911505</v>
+        <v>69.73321568525679</v>
       </c>
       <c r="C14" t="n">
-        <v>88.97396982920753</v>
+        <v>69.10775577610897</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2819476975157159</v>
+        <v>0.7912412422398727</v>
       </c>
       <c r="E14" t="n">
-        <v>89.64601769911505</v>
+        <v>69.73321568525679</v>
       </c>
     </row>
     <row r="15">
@@ -2853,16 +2892,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>92.03539823008849</v>
+        <v>55.45930328117025</v>
       </c>
       <c r="C15" t="n">
-        <v>91.95853736173055</v>
+        <v>53.5995658744995</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2274177166982554</v>
+        <v>1.101898068189621</v>
       </c>
       <c r="E15" t="n">
-        <v>92.03539823008849</v>
+        <v>55.45930328117025</v>
       </c>
     </row>
     <row r="16">
@@ -2872,16 +2911,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>89.73451327433628</v>
+        <v>53.34916392010312</v>
       </c>
       <c r="C16" t="n">
-        <v>89.359740995796</v>
+        <v>52.36321234148576</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2631288017049277</v>
+        <v>1.039600084225337</v>
       </c>
       <c r="E16" t="n">
-        <v>89.73451327433628</v>
+        <v>53.34916392010312</v>
       </c>
     </row>
     <row r="17">
@@ -2891,16 +2930,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>93.98230088495575</v>
+        <v>66.85274094066557</v>
       </c>
       <c r="C17" t="n">
-        <v>93.61759464751323</v>
+        <v>65.88050769130022</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1735694931826098</v>
+        <v>0.7923989641169706</v>
       </c>
       <c r="E17" t="n">
-        <v>93.98230088495575</v>
+        <v>66.85274094066558</v>
       </c>
     </row>
     <row r="18">
@@ -2910,16 +2949,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>89.14454277286136</v>
+        <v>64.11266533447521</v>
       </c>
       <c r="C18" t="n">
-        <v>87.91780436874288</v>
+        <v>60.43250743271322</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3559372454917138</v>
+        <v>0.8781754391267895</v>
       </c>
       <c r="E18" t="n">
-        <v>89.14454277286136</v>
+        <v>64.11266533447522</v>
       </c>
     </row>
     <row r="19">
@@ -2929,16 +2968,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>94.95575221238938</v>
+        <v>74.70791269820673</v>
       </c>
       <c r="C19" t="n">
-        <v>94.88627356909927</v>
+        <v>74.26351112868397</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1451164108374542</v>
+        <v>0.6834208283573389</v>
       </c>
       <c r="E19" t="n">
-        <v>94.95575221238938</v>
+        <v>74.70791269820673</v>
       </c>
     </row>
     <row r="20">
@@ -2948,16 +2987,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>90.02949852507375</v>
+        <v>57.89176376958278</v>
       </c>
       <c r="C20" t="n">
-        <v>89.19677419510818</v>
+        <v>55.20133329169587</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3220054106389095</v>
+        <v>1.144871973494689</v>
       </c>
       <c r="E20" t="n">
-        <v>90.02949852507375</v>
+        <v>57.89176376958278</v>
       </c>
     </row>
     <row r="21">
@@ -2967,16 +3006,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>86.22418879056048</v>
+        <v>59.83468715127295</v>
       </c>
       <c r="C21" t="n">
-        <v>84.83230667544817</v>
+        <v>55.86572470078268</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3812473995962743</v>
+        <v>1.068474035958449</v>
       </c>
       <c r="E21" t="n">
-        <v>86.22418879056048</v>
+        <v>59.83468715127293</v>
       </c>
     </row>
     <row r="22">
@@ -2986,16 +3025,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>91.85840707964601</v>
+        <v>63.6632669832784</v>
       </c>
       <c r="C22" t="n">
-        <v>90.82272801323084</v>
+        <v>62.57095422084024</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3034399851002187</v>
+        <v>0.8541419580578804</v>
       </c>
       <c r="E22" t="n">
-        <v>91.85840707964601</v>
+        <v>63.6632669832784</v>
       </c>
     </row>
     <row r="23">
@@ -3005,16 +3044,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>91.26843657817109</v>
+        <v>55.89624477720396</v>
       </c>
       <c r="C23" t="n">
-        <v>90.77071109295449</v>
+        <v>54.5931483630079</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2503151584794978</v>
+        <v>1.054583060741425</v>
       </c>
       <c r="E23" t="n">
-        <v>91.26843657817109</v>
+        <v>55.89624477720395</v>
       </c>
     </row>
     <row r="24">
@@ -3024,16 +3063,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>92.83185840707965</v>
+        <v>61.92960146714072</v>
       </c>
       <c r="C24" t="n">
-        <v>92.61236259920224</v>
+        <v>61.30782524345081</v>
       </c>
       <c r="D24" t="n">
-        <v>0.20492224970385</v>
+        <v>0.9710769653320312</v>
       </c>
       <c r="E24" t="n">
-        <v>92.83185840707964</v>
+        <v>61.92960146714072</v>
       </c>
     </row>
     <row r="25">
@@ -3043,16 +3082,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>90.26548672566372</v>
+        <v>59.44809211152345</v>
       </c>
       <c r="C25" t="n">
-        <v>90.02544485390993</v>
+        <v>58.09033039658252</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3021294937459364</v>
+        <v>0.9475799530744553</v>
       </c>
       <c r="E25" t="n">
-        <v>90.26548672566371</v>
+        <v>59.44809211152345</v>
       </c>
     </row>
     <row r="26">
@@ -3062,16 +3101,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>92.30088495575221</v>
+        <v>68.40941530636078</v>
       </c>
       <c r="C26" t="n">
-        <v>91.71153374375049</v>
+        <v>67.54566515778524</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2189763761988919</v>
+        <v>0.77194762652119</v>
       </c>
       <c r="E26" t="n">
-        <v>92.30088495575221</v>
+        <v>68.40941530636078</v>
       </c>
     </row>
     <row r="27">
@@ -3081,16 +3120,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>84.77876106194689</v>
+        <v>63.91975709132432</v>
       </c>
       <c r="C27" t="n">
-        <v>84.00065603074184</v>
+        <v>64.36833608877882</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7079357983184915</v>
+        <v>1.091164549502234</v>
       </c>
       <c r="E27" t="n">
-        <v>84.77876106194689</v>
+        <v>63.91975709132431</v>
       </c>
     </row>
     <row r="28">
@@ -3100,16 +3139,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>84.66076696165192</v>
+        <v>61.00234431093695</v>
       </c>
       <c r="C28" t="n">
-        <v>83.26062967090959</v>
+        <v>59.39032556184499</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5882024137157714</v>
+        <v>0.9603426352143287</v>
       </c>
       <c r="E28" t="n">
-        <v>84.66076696165192</v>
+        <v>61.00234431093695</v>
       </c>
     </row>
     <row r="29">
@@ -3119,16 +3158,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>98.49557522123894</v>
+        <v>77.63518715559823</v>
       </c>
       <c r="C29" t="n">
-        <v>98.494388851445</v>
+        <v>77.0787971495926</v>
       </c>
       <c r="D29" t="n">
-        <v>0.05846711391413919</v>
+        <v>0.5440194218109051</v>
       </c>
       <c r="E29" t="n">
-        <v>98.49557522123894</v>
+        <v>77.63518715559823</v>
       </c>
     </row>
     <row r="30">
@@ -3138,16 +3177,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>98.23026150745248</v>
+        <v>77.9886504208514</v>
       </c>
       <c r="C30" t="n">
-        <v>98.24125436132897</v>
+        <v>77.56445761092485</v>
       </c>
       <c r="D30" t="n">
-        <v>0.04900147903698174</v>
+        <v>0.4763231809561451</v>
       </c>
       <c r="E30" t="n">
-        <v>98.23026150745248</v>
+        <v>77.98865042085139</v>
       </c>
     </row>
     <row r="31">
@@ -3157,16 +3196,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>96.54867256637168</v>
+        <v>90.63244491734358</v>
       </c>
       <c r="C31" t="n">
-        <v>96.48129149868096</v>
+        <v>90.50467616785814</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1163393856260645</v>
+        <v>0.2525829322015246</v>
       </c>
       <c r="E31" t="n">
-        <v>96.54867256637168</v>
+        <v>90.63244491734358</v>
       </c>
     </row>
     <row r="32">
@@ -3176,16 +3215,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>91.80138236489937</v>
+        <v>65.12390822296616</v>
       </c>
       <c r="C32" t="n">
-        <v>91.34415628368239</v>
+        <v>64.00995050342915</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2517985150988956</v>
+        <v>0.8473526093772509</v>
       </c>
       <c r="E32" t="n">
-        <v>91.80138236489937</v>
+        <v>65.12390822296616</v>
       </c>
     </row>
     <row r="33">
@@ -3195,16 +3234,665 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.520713838592158</v>
+        <v>8.154028567790915</v>
       </c>
       <c r="C33" t="n">
-        <v>3.857255239968123</v>
+        <v>8.668626105717335</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1415336286522811</v>
+        <v>0.1978767105001035</v>
       </c>
       <c r="E33" t="n">
-        <v>3.520713838592159</v>
+        <v>8.154028567790915</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>f1_score</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sub6ex1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>45.91458403619409</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.16392732845596</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.277435113986333</v>
+      </c>
+      <c r="E2" t="n">
+        <v>45.91458403619409</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sub6ex2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>54.87919445669945</v>
+      </c>
+      <c r="C3" t="n">
+        <v>52.61539956008384</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.023578230539958</v>
+      </c>
+      <c r="E3" t="n">
+        <v>54.87919445669945</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sub6ex3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>48.51010821892923</v>
+      </c>
+      <c r="C4" t="n">
+        <v>45.47926378933381</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.150785983105501</v>
+      </c>
+      <c r="E4" t="n">
+        <v>48.51010821892923</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sub7ex1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>39.71453040251213</v>
+      </c>
+      <c r="C5" t="n">
+        <v>36.30012391775552</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.149472715457281</v>
+      </c>
+      <c r="E5" t="n">
+        <v>39.71453040251213</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sub7ex2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>46.08309760465056</v>
+      </c>
+      <c r="C6" t="n">
+        <v>44.53255996093846</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.060574432214101</v>
+      </c>
+      <c r="E6" t="n">
+        <v>46.08309760465055</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sub7ex3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>39.8441162985839</v>
+      </c>
+      <c r="C7" t="n">
+        <v>38.91089572023083</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.165548644463221</v>
+      </c>
+      <c r="E7" t="n">
+        <v>39.8441162985839</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sub8ex1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>62.61914030398187</v>
+      </c>
+      <c r="C8" t="n">
+        <v>61.08877515385639</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.9490195490031814</v>
+      </c>
+      <c r="E8" t="n">
+        <v>62.61914030398187</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sub8ex2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>59.07810621199145</v>
+      </c>
+      <c r="C9" t="n">
+        <v>55.70834134001118</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.9238175241897503</v>
+      </c>
+      <c r="E9" t="n">
+        <v>59.07810621199145</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sub8ex3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>61.0487979999827</v>
+      </c>
+      <c r="C10" t="n">
+        <v>58.86982632252129</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8512742754537612</v>
+      </c>
+      <c r="E10" t="n">
+        <v>61.0487979999827</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sub9ex1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>48.62256593915173</v>
+      </c>
+      <c r="C11" t="n">
+        <v>46.89908213667028</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.101410766442617</v>
+      </c>
+      <c r="E11" t="n">
+        <v>48.62256593915173</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sub9ex2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>55.79425427555602</v>
+      </c>
+      <c r="C12" t="n">
+        <v>53.52341558048422</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.032007731000582</v>
+      </c>
+      <c r="E12" t="n">
+        <v>55.79425427555602</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sub9ex3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>53.0109257000493</v>
+      </c>
+      <c r="C13" t="n">
+        <v>49.37764993422827</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.172614520788193</v>
+      </c>
+      <c r="E13" t="n">
+        <v>53.0109257000493</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sub10ex1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>57.12497512954265</v>
+      </c>
+      <c r="C14" t="n">
+        <v>55.06515964708369</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.207915077606837</v>
+      </c>
+      <c r="E14" t="n">
+        <v>57.12497512954265</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sub10ex2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>46.44607652315332</v>
+      </c>
+      <c r="C15" t="n">
+        <v>42.49101179547583</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.267249787847201</v>
+      </c>
+      <c r="E15" t="n">
+        <v>46.44607652315331</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sub10ex3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>43.90608915302035</v>
+      </c>
+      <c r="C16" t="n">
+        <v>37.81372986063495</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.431303917368253</v>
+      </c>
+      <c r="E16" t="n">
+        <v>43.90608915302035</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sub11ex1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>39.2097682505904</v>
+      </c>
+      <c r="C17" t="n">
+        <v>32.90901545034841</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.38226335744063</v>
+      </c>
+      <c r="E17" t="n">
+        <v>39.2097682505904</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sub11ex2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>56.46605939497747</v>
+      </c>
+      <c r="C18" t="n">
+        <v>54.9495838707991</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.9194589624802271</v>
+      </c>
+      <c r="E18" t="n">
+        <v>56.46605939497747</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sub11ex3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>62.40451907023417</v>
+      </c>
+      <c r="C19" t="n">
+        <v>59.59772856951552</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.9877563034494719</v>
+      </c>
+      <c r="E19" t="n">
+        <v>62.40451907023417</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sub12ex1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>51.36601527694876</v>
+      </c>
+      <c r="C20" t="n">
+        <v>46.35074967428913</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.352468975881735</v>
+      </c>
+      <c r="E20" t="n">
+        <v>51.36601527694876</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sub12ex2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>54.77547383627886</v>
+      </c>
+      <c r="C21" t="n">
+        <v>51.65841054640381</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.448145973309874</v>
+      </c>
+      <c r="E21" t="n">
+        <v>54.77547383627886</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sub12ex3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>58.93909116860873</v>
+      </c>
+      <c r="C22" t="n">
+        <v>58.17787193097591</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.9245756586392722</v>
+      </c>
+      <c r="E22" t="n">
+        <v>58.93909116860873</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sub13ex1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>32.40616268306819</v>
+      </c>
+      <c r="C23" t="n">
+        <v>26.2347546684501</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.653718775510788</v>
+      </c>
+      <c r="E23" t="n">
+        <v>32.40616268306819</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sub13ex2</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>39.54221057275582</v>
+      </c>
+      <c r="C24" t="n">
+        <v>34.75960746174958</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.525027164320151</v>
+      </c>
+      <c r="E24" t="n">
+        <v>39.54221057275582</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sub13ex3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>47.41381845863718</v>
+      </c>
+      <c r="C25" t="n">
+        <v>43.81659566309211</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.310593683520953</v>
+      </c>
+      <c r="E25" t="n">
+        <v>47.41381845863718</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sub14ex1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>61.00727514943901</v>
+      </c>
+      <c r="C26" t="n">
+        <v>57.59171523847344</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.048967830091715</v>
+      </c>
+      <c r="E26" t="n">
+        <v>61.00727514943901</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sub14ex2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>52.74405487936747</v>
+      </c>
+      <c r="C27" t="n">
+        <v>50.80302738173484</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.357616215199232</v>
+      </c>
+      <c r="E27" t="n">
+        <v>52.74405487936747</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sub14ex3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>50.74455661381154</v>
+      </c>
+      <c r="C28" t="n">
+        <v>47.93650960722079</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.038203216592471</v>
+      </c>
+      <c r="E28" t="n">
+        <v>50.74455661381154</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sub15ex1</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>67.7068140727861</v>
+      </c>
+      <c r="C29" t="n">
+        <v>66.04537008813516</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.7346151414016882</v>
+      </c>
+      <c r="E29" t="n">
+        <v>67.7068140727861</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sub15ex2</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>70.71479857092189</v>
+      </c>
+      <c r="C30" t="n">
+        <v>69.735538255203</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.6617666813234488</v>
+      </c>
+      <c r="E30" t="n">
+        <v>70.71479857092189</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sub15ex3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>65.29450946807499</v>
+      </c>
+      <c r="C31" t="n">
+        <v>64.12652996197066</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.8254706541697183</v>
+      </c>
+      <c r="E31" t="n">
+        <v>65.29450946807499</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>52.44438965734997</v>
+      </c>
+      <c r="C32" t="n">
+        <v>49.4510723472042</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.131155228759938</v>
+      </c>
+      <c r="E32" t="n">
+        <v>52.44438965734997</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>9.209824499574564</v>
+      </c>
+      <c r="C33" t="n">
+        <v>10.29354281843498</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.2338060840685769</v>
+      </c>
+      <c r="E33" t="n">
+        <v>9.209824499574564</v>
       </c>
     </row>
   </sheetData>
